--- a/docs/Mapping_casi_uso/matrimoni/Matr_004.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_004.xlsx
@@ -857,7 +857,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -866,7 +866,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -875,7 +875,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -884,7 +884,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -893,13 +893,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -908,7 +908,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -917,13 +917,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -932,7 +932,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Interprete</t>
@@ -1043,13 +1043,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1153,7 +1153,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="33.79296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9832,10 +9832,10 @@
         <v>279</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>280</v>
@@ -10476,10 +10476,10 @@
         <v>282</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>283</v>
@@ -11120,10 +11120,10 @@
         <v>285</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>286</v>
@@ -11764,10 +11764,10 @@
         <v>288</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D462" s="2" t="s">
         <v>289</v>
@@ -12408,10 +12408,10 @@
         <v>291</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D490" s="2" t="s">
         <v>292</v>
@@ -13052,10 +13052,10 @@
         <v>294</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>292</v>
@@ -13857,10 +13857,10 @@
         <v>299</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>300</v>
@@ -14501,10 +14501,10 @@
         <v>302</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>300</v>
@@ -15686,7 +15686,7 @@
         <v>344</v>
       </c>
       <c r="F632" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G632" s="2" t="s">
         <v>55</v>
